--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>
@@ -554,7 +554,7 @@
 この患者状態の臨床的ステータス（アクティブか否かなど）</t>
   </si>
   <si>
-    <t>診断の場合、転帰区分を指定するのに使用する。使用する場合、ConditionClinicalStatusCodesは必須で、それ以外にHL7表0241、JHSD表0006、レセプト電算システム転帰区分コードが使用できる。</t>
+    <t>データ型はCodeableConceptである。clinicalStatusには何らかの臨床的判断が伴うため、FHIRで指定されたvalue setよりも特異性のあるvalue setが必要となりうる。これは、いわゆる転帰(outcome)のみを意味しない。使用する場合、ConditionClinicalStatusCodesを必須として指定し、それ以外にHL7表0241、JHSD表0006、レセプト電算システム転帰区分コードが使用できる。</t>
   </si>
   <si>
     <t>required</t>
@@ -1016,7 +1016,7 @@
     <t>medisRecordNo</t>
   </si>
   <si>
-    <t>MEDIS ICD10対応標準病名マスター(管理番号)。【詳細参照】</t>
+    <t>MEDIS ICD10対応標準病名マスターの交換用コード。</t>
   </si>
   <si>
     <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>
@@ -1169,7 +1169,10 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1227,7 +1230,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
+    <t>通常、イベントが発生した受療行動の中で行われることが多いですが、公式的に受療行動が完了する前または後に開始される場合がありますが、それでも受療行動の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の受療行動とは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1455,7 +1458,7 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>演出の種類</t>
+    <t>ステージングの種類</t>
   </si>
   <si>
     <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
@@ -1502,10 +1505,10 @@
     <t>Condition.evidence.code</t>
   </si>
   <si>
-    <t>表れ/症状</t>
-  </si>
-  <si>
-    <t>この状態の記録に至った兆候や症状。</t>
+    <t>徴候や症状</t>
+  </si>
+  <si>
+    <t>この状態の記録に至った徴候や症状。</t>
   </si>
   <si>
     <t>症状や現れ方を記述するコード。</t>
@@ -1906,8 +1909,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5567,7 +5570,7 @@
         <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>317</v>
@@ -8610,9 +8613,11 @@
       <c r="X56" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y56" s="2"/>
+      <c r="Y56" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8648,31 +8653,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8691,17 +8696,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8750,7 +8755,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8765,19 +8770,19 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8785,10 +8790,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8811,16 +8816,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8870,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8885,19 +8890,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8905,10 +8910,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8931,16 +8936,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8990,7 +8995,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9005,19 +9010,19 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9025,10 +9030,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9051,16 +9056,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9110,7 +9115,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9119,7 +9124,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9134,10 +9139,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9145,10 +9150,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9171,13 +9176,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9228,7 +9233,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9249,13 +9254,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9263,10 +9268,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9289,13 +9294,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9346,7 +9351,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9370,10 +9375,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9407,13 +9412,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9464,7 +9469,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9485,13 +9490,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9499,10 +9504,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9525,13 +9530,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9582,7 +9587,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9594,7 +9599,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9606,7 +9611,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9622,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9646,10 +9651,10 @@
         <v>228</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9735,10 +9740,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9764,10 +9769,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>155</v>
@@ -9855,14 +9860,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9884,10 +9889,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>155</v>
@@ -9942,7 +9947,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9977,10 +9982,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10006,10 +10011,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10039,10 +10044,10 @@
         <v>218</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10060,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10069,7 +10074,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10078,7 +10083,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>178</v>
@@ -10095,10 +10100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10121,13 +10126,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10178,7 +10183,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10187,7 +10192,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10202,7 +10207,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10213,10 +10218,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10242,10 +10247,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10275,10 +10280,10 @@
         <v>218</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10296,7 +10301,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10320,7 +10325,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10331,10 +10336,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10357,16 +10362,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10416,7 +10421,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10428,7 +10433,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10440,7 +10445,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10451,10 +10456,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10480,10 +10485,10 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10569,10 +10574,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10598,10 +10603,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>155</v>
@@ -10689,14 +10694,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10718,10 +10723,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>155</v>
@@ -10776,7 +10781,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10811,10 +10816,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10840,10 +10845,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10873,10 +10878,10 @@
         <v>218</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10894,7 +10899,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10903,13 +10908,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>198</v>
@@ -10918,10 +10923,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10929,10 +10934,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10955,13 +10960,13 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11012,7 +11017,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11021,7 +11026,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11036,10 +11041,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11047,10 +11052,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11073,13 +11078,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11130,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11145,16 +11150,16 @@
         <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1885,17 +1885,17 @@
   <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.16796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1904,28 +1904,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -380,7 +380,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -637,7 +637,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -710,7 +710,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1172,7 +1172,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1429,7 +1429,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1467,7 +1467,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1514,7 +1514,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1533,7 +1533,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
